--- a/results/monthly_investor_report_2026-09-24.xlsx
+++ b/results/monthly_investor_report_2026-09-24.xlsx
@@ -627,7 +627,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2262039331984107</v>
+        <v>0.2262039331984106</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22620.39331984107</v>
+        <v>22620.39331984106</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.0485933057984229</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1099.19968987164</v>
+        <v>1099.199689871639</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>443.2928200262833</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1899558085524913</v>
+        <v>0.1899558085524912</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18995.58085524913</v>
+        <v>18995.58085524912</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.0955196579070878</v>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.183840258249098</v>
+        <v>0.1838402582490981</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18384.0258249098</v>
+        <v>18384.02582490982</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>427.7609667454678</v>
+        <v>427.7609667454736</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>221.0259050817818</v>
@@ -1060,7 +1060,7 @@
         <v>205.2</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.4653615816464586</v>
+        <v>0.4653615816464639</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1356,13 +1356,13 @@
         <v>422.75</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0340045699699408</v>
+        <v>-0.0340045699699409</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.0485933057984229</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0801730736352934</v>
+        <v>0.0801730736352933</v>
       </c>
       <c r="H8" s="14" t="n">
         <v>408.3745680452075</v>
@@ -1371,7 +1371,7 @@
         <v>443.2928200262833</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>456.6431668793203</v>
+        <v>456.6431668793202</v>
       </c>
       <c r="K8" s="14" t="n">
         <v>401.6125</v>
@@ -1416,7 +1416,7 @@
         <v>-0.0120987386157355</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>0.0914169657590902</v>
@@ -1470,7 +1470,7 @@
         <v>410.75</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>-0.08640226646425481</v>
+        <v>-0.0864022664642549</v>
       </c>
       <c r="F10" s="18" t="n">
         <v>0.0228858964847257</v>
@@ -1527,7 +1527,7 @@
         <v>22</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>-0.0753137768113169</v>
+        <v>-0.075313776811317</v>
       </c>
       <c r="F11" s="21" t="n">
         <v>-0.0031957788743339</v>
@@ -1641,7 +1641,7 @@
         <v>86.44999694824219</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>-0.0445633254802306</v>
+        <v>-0.0445633254802305</v>
       </c>
       <c r="F13" s="21" t="n">
         <v>-0.0062980681240358</v>
@@ -1728,7 +1728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1882,7 +1882,7 @@
         <v>0.0208981225974997</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
     </row>
     <row r="6">
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="E7" s="21" t="n">
-        <v>0.088031688778045</v>
+        <v>0.08803168877804519</v>
       </c>
       <c r="F7" s="21" t="n">
         <v>0.1235955099960948</v>
@@ -1997,7 +1997,7 @@
         <v>-0.1026086779608242</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.2463485508681537</v>
+        <v>-0.2463485508681538</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>0.0294478279074266</v>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="J8" s="15" t="n">
-        <v>0.0186115303364237</v>
+        <v>0.0186115303364236</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>0.0955196579070878</v>
@@ -2034,13 +2034,13 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>-0.0196382977066572</v>
+        <v>-0.0196382977066574</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>-0.09924027566894179</v>
+        <v>-0.099240275668942</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>0.4295862429600472</v>
+        <v>0.429586242960047</v>
       </c>
       <c r="H9" s="23" t="n">
         <v>-0.0463635917944209</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="J9" s="23" t="n">
-        <v>0.0260406298593469</v>
+        <v>0.026040629859347</v>
       </c>
       <c r="K9" s="23" t="n">
         <v>0.012842734528077</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="J10" s="23" t="n">
-        <v>0.0213838784267614</v>
+        <v>0.0213838784267613</v>
       </c>
       <c r="K10" s="23" t="n">
         <v>0.01715475009491</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="J11" s="23" t="n">
-        <v>0.0246367814914132</v>
+        <v>0.0246367814914131</v>
       </c>
       <c r="K11" s="23" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>-0.1695485281901001</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>-0.2232704889680877</v>
+        <v>-0.2232704889680876</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>0.1048848031430502</v>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="J12" s="21" t="n">
-        <v>0.0147205548238683</v>
+        <v>0.0147205548238684</v>
       </c>
       <c r="K12" s="21" t="n">
         <v>-0.0062980681240358</v>
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>-0.0612027694175202</v>
+        <v>-0.0612027694175204</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>-0.09492047500948481</v>
+        <v>-0.0949204750094849</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>-0.0037021562789459</v>
@@ -2226,7 +2226,7 @@
         <v>0.0202362846087154</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>0.0444883459564572</v>
+        <v>0.0444883459564573</v>
       </c>
     </row>
     <row r="14">
@@ -2292,13 +2292,13 @@
         </is>
       </c>
       <c r="E15" s="25" t="n">
-        <v>-0.0391304642681914</v>
+        <v>-0.0391304642681913</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>-0.1032462075752526</v>
+        <v>-0.1032462075752523</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>-0.0617924816203567</v>
+        <v>-0.0617924816203565</v>
       </c>
       <c r="H15" s="25" t="n">
         <v>0.1755718149091731</v>
@@ -2312,7 +2312,7 @@
         <v>0.0205927546794307</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>0.0138761110298257</v>
+        <v>0.0138761110298255</v>
       </c>
     </row>
     <row r="16">
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="J16" s="25" t="n">
-        <v>0.0232585633457884</v>
+        <v>0.0232585633457885</v>
       </c>
       <c r="K16" s="25" t="n">
         <v>0.0218373705587808</v>
@@ -2560,7 +2560,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2679,7 +2679,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2930,7 +2930,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3055,7 +3055,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3246,10 +3246,10 @@
         <v>37.93999862670898</v>
       </c>
       <c r="E8" s="27" t="n">
-        <v>-0.02367478047330518</v>
+        <v>-0.0236747804733054</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>-5153.556888308289</v>
+        <v>-5153.556888308318</v>
       </c>
       <c r="G8" s="26" t="n">
         <v>20753084.26775555</v>

--- a/results/monthly_investor_report_2026-09-24.xlsx
+++ b/results/monthly_investor_report_2026-09-24.xlsx
@@ -627,7 +627,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1159,7 +1159,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1728,7 +1728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2560,7 +2560,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2679,7 +2679,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2930,7 +2930,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3055,7 +3055,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
